--- a/ig/DM-OCTOBRE-2025/ValueSet-JDV-J65-SubjectRole-DMP.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-JDV-J65-SubjectRole-DMP.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="886">
   <si>
     <t>Property</t>
   </si>
@@ -2480,6 +2480,12 @@
   </si>
   <si>
     <t>Gérant d'antenne</t>
+  </si>
+  <si>
+    <t>FON-62</t>
+  </si>
+  <si>
+    <t>Consultations de solidarité territoriale</t>
   </si>
   <si>
     <t>FON-AU</t>
@@ -3070,7 +3076,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -3415,18 +3421,26 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>38</v>
+        <v>821</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>38</v>
+        <v>822</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B44" t="s" s="2">
-        <v>821</v>
+      <c r="B45" t="s" s="2">
+        <v>823</v>
       </c>
     </row>
   </sheetData>
@@ -3453,111 +3467,111 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>54</v>
@@ -3565,7 +3579,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>56</v>
@@ -3573,7 +3587,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>58</v>
@@ -3581,7 +3595,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>60</v>
@@ -3589,7 +3603,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>62</v>
@@ -3597,7 +3611,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>114</v>
@@ -3605,7 +3619,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>116</v>
@@ -3613,7 +3627,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>118</v>
@@ -3621,7 +3635,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>120</v>
@@ -3629,7 +3643,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>122</v>
@@ -3637,7 +3651,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>124</v>
@@ -3645,7 +3659,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>126</v>
@@ -3653,7 +3667,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>128</v>
@@ -3661,7 +3675,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>130</v>
@@ -3669,7 +3683,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>132</v>
@@ -3677,7 +3691,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>134</v>
@@ -3685,7 +3699,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>109</v>
@@ -3693,74 +3707,74 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="41">
@@ -3776,7 +3790,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-OCTOBRE-2025/ValueSet-JDV-J65-SubjectRole-DMP.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-JDV-J65-SubjectRole-DMP.xlsx
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20251028120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2025-10-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
